--- a/Code/Jupiter/Connect4/round_robin_out/round_robin_results.xlsx
+++ b/Code/Jupiter/Connect4/round_robin_out/round_robin_results.xlsx
@@ -480,10 +480,10 @@
         <v>0.5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.535</v>
+        <v>0.52</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.495</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.465</v>
+        <v>0.48</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0.5</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.505</v>
+        <v>0.485</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0.485</v>
@@ -639,11 +639,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V00 D1.5 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V00 D1.5 FN0.25 FF0.125 CB3 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.515</v>
+        <v>0.5175000000000001</v>
       </c>
       <c r="D2" t="n">
         <v>1.5</v>
@@ -652,34 +652,34 @@
         <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.25</v>
       </c>
-      <c r="L2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.1</v>
-      </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
         <v>1000</v>
@@ -691,52 +691,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V02</t>
+          <t>V01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V02 D0.5 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V01 D1.5 FN0.25 FF0.125 CB2 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.495</v>
+        <v>0.4975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.25</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.1</v>
-      </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
         <v>1000</v>
@@ -748,52 +748,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V01</t>
+          <t>V02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V01 D1 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V02 D1.5 FN0.25 FF0.125 CB4 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.49</v>
+        <v>0.485</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.25</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.1</v>
-      </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
         <v>1000</v>
@@ -872,28 +872,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>V00 D1.5 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V00 D1.5 FN0.25 FF0.125 CB3 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>V01 D1 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V01 D1.5 FN0.25 FF0.125 CB2 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
         <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>0.535</v>
+        <v>0.52</v>
       </c>
       <c r="I2" t="n">
-        <v>0.465</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="3">
@@ -905,28 +905,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>V00 D1.5 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V00 D1.5 FN0.25 FF0.125 CB3 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>V02 D0.5 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V02 D1.5 FN0.25 FF0.125 CB4 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>0.495</v>
+        <v>0.515</v>
       </c>
       <c r="I3" t="n">
-        <v>0.505</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="4">
@@ -938,12 +938,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V01 D1 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V01 D1.5 FN0.25 FF0.125 CB2 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>V02 D0.5 FN0.25 FF0.1 CB7 PB1 VM1.1 V30 TW0.25 PM0.2 PU0.1 TS0.5 W21 W31000</t>
+          <t>V02 D1.5 FN0.25 FF0.125 CB4 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
       <c r="E4" t="n">

--- a/Code/Jupiter/Connect4/round_robin_out/round_robin_results.xlsx
+++ b/Code/Jupiter/Connect4/round_robin_out/round_robin_results.xlsx
@@ -68,15 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -444,13 +441,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,16 +454,6 @@
           <t>V00</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>V01</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>V02</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -479,47 +464,9 @@
       <c r="B2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.515</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>V01</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.515</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>V02</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.5</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:D4">
+  <conditionalFormatting sqref="B2">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -541,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,9 +589,7 @@
           <t>V00 D1.5 FN0.25 FF0.125 CB3 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.5175000000000001</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>1.5</v>
       </c>
@@ -685,120 +630,6 @@
         <v>1000</v>
       </c>
       <c r="Q2" t="n">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>V01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>V01 D1.5 FN0.25 FF0.125 CB2 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.4975</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>75</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N3" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>10</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>V02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>V02 D1.5 FN0.25 FF0.125 CB4 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>75</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Q4" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -813,156 +644,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>j</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name_i</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>name_j</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>points_i</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>points_j</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>games</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ppg_i</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ppg_j</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>V00 D1.5 FN0.25 FF0.125 CB3 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>V01 D1.5 FN0.25 FF0.125 CB2 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>104</v>
-      </c>
-      <c r="F2" t="n">
-        <v>96</v>
-      </c>
-      <c r="G2" t="n">
-        <v>200</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>V00 D1.5 FN0.25 FF0.125 CB3 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>V02 D1.5 FN0.25 FF0.125 CB4 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>103</v>
-      </c>
-      <c r="F3" t="n">
-        <v>97</v>
-      </c>
-      <c r="G3" t="n">
-        <v>200</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.485</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>V01 D1.5 FN0.25 FF0.125 CB2 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>V02 D1.5 FN0.25 FF0.125 CB4 PB0.75 VM0.8 V30 TW75 PM0.5 PU0.25 TS9 W210 W31000</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>103</v>
-      </c>
-      <c r="F4" t="n">
-        <v>97</v>
-      </c>
-      <c r="G4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.485</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>